--- a/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/practice_start.xlsx
+++ b/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/practice_start.xlsx
@@ -440,7 +440,7 @@
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -500,12 +500,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -572,12 +572,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Mutare</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chitungwiza</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Mutare</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chitungwiza</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
